--- a/data/trans_camb/IP11-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP11-Edad-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 8,38</t>
+          <t>-0,59; 8,22</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,01; 0,11</t>
+          <t>-6,0; -0,11</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,44; 0,98</t>
+          <t>-5,46; 1,1</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,56; 5,95</t>
+          <t>-5,06; 5,13</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-7,61; 0,14</t>
+          <t>-7,85; -0,09</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-7,53; 1,09</t>
+          <t>-8,03; 0,73</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 5,39</t>
+          <t>-0,96; 5,45</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-6,02; -1,0</t>
+          <t>-5,95; -0,94</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-5,58; 0,23</t>
+          <t>-5,46; -0,0</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-15,16; 573,0</t>
+          <t>-20,59; 487,35</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 230,29</t>
+          <t>-100,0; 63,14</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 161,95</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-46,47; 153,3</t>
+          <t>-59,01; 152,15</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-91,6; 23,17</t>
+          <t>-92,43; 19,63</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 99,01</t>
+          <t>-100,0; 60,91</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-19,37; 174,9</t>
+          <t>-16,84; 191,39</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-90,15; -21,33</t>
+          <t>-88,74; -7,65</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-90,09; 27,37</t>
+          <t>-88,74; 31,45</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 6,25</t>
+          <t>-0,9; 6,5</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,25; 0,9</t>
+          <t>-5,1; 1,02</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,63; 0,15</t>
+          <t>-5,78; 0,25</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,34; 8,72</t>
+          <t>0,04; 8,16</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-5,02; 1,47</t>
+          <t>-4,87; 1,34</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-6,45; 0,21</t>
+          <t>-6,74; 0,23</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,86; 6,2</t>
+          <t>0,91; 6,21</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-4,06; 0,26</t>
+          <t>-4,33; 0,11</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-5,32; -0,75</t>
+          <t>-5,36; -0,73</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-12,66; 163,16</t>
+          <t>-14,78; 176,69</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-75,15; 37,57</t>
+          <t>-74,63; 31,06</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-84,05; 16,87</t>
+          <t>-83,62; 17,81</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,79; 187,57</t>
+          <t>-2,15; 165,13</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-61,27; 34,87</t>
+          <t>-63,75; 30,01</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-82,28; 11,37</t>
+          <t>-84,62; 7,42</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>12,2; 132,7</t>
+          <t>11,25; 136,24</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-58,47; 6,51</t>
+          <t>-61,22; 2,73</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-77,01; -12,17</t>
+          <t>-77,4; -11,2</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,14; 4,88</t>
+          <t>-5,0; 5,18</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-7,94; 0,21</t>
+          <t>-8,11; 0,2</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-8,99; -0,22</t>
+          <t>-8,77; 0,05</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,21; 5,37</t>
+          <t>-5,16; 5,45</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-6,51; 3,04</t>
+          <t>-6,31; 2,95</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-8,64; 0,68</t>
+          <t>-9,32; 0,33</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-3,68; 3,65</t>
+          <t>-3,83; 3,37</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-5,92; 0,43</t>
+          <t>-5,95; 0,58</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-7,39; -0,94</t>
+          <t>-7,46; -0,99</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-55,61; 119,56</t>
+          <t>-53,35; 115,32</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-80,7; 13,28</t>
+          <t>-80,86; 12,27</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-87,02; 2,27</t>
+          <t>-83,54; 24,39</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-51,61; 104,11</t>
+          <t>-50,28; 115,9</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-59,98; 61,26</t>
+          <t>-60,87; 59,96</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-81,47; 22,39</t>
+          <t>-82,63; 22,92</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-40,17; 65,89</t>
+          <t>-41,64; 58,62</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-61,93; 11,06</t>
+          <t>-60,86; 14,48</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-77,25; -13,66</t>
+          <t>-76,39; -13,04</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,97; 6,26</t>
+          <t>-1,93; 6,21</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,99; 4,9</t>
+          <t>-2,46; 4,73</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-5,82; 0,51</t>
+          <t>-5,42; 0,97</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,31; 11,47</t>
+          <t>2,29; 12,06</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 6,78</t>
+          <t>-1,8; 6,73</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-7,05; 0,19</t>
+          <t>-6,18; 0,14</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,49; 7,73</t>
+          <t>1,41; 7,67</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 4,37</t>
+          <t>-1,4; 4,33</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-4,89; -0,55</t>
+          <t>-4,72; -0,51</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-32,61; 202,36</t>
+          <t>-31,42; 177,45</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-46,32; 154,32</t>
+          <t>-41,47; 140,52</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-79,53; 19,78</t>
+          <t>-77,41; 37,91</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>25,58; 269,89</t>
+          <t>24,2; 274,51</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-25,06; 164,14</t>
+          <t>-24,63; 155,52</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-80,27; 14,54</t>
+          <t>-77,81; 11,24</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>19,33; 174,19</t>
+          <t>16,53; 173,73</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-22,66; 99,59</t>
+          <t>-23,45; 98,59</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-69,65; -8,71</t>
+          <t>-69,98; -8,63</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,05; 4,07</t>
+          <t>0,04; 4,16</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,79; -0,17</t>
+          <t>-3,55; -0,04</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-4,36; -1,01</t>
+          <t>-4,38; -0,85</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,08; 5,69</t>
+          <t>0,93; 5,68</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,94; 1,02</t>
+          <t>-2,93; 1,11</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-5,2; -1,38</t>
+          <t>-5,04; -1,29</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,08; 4,21</t>
+          <t>1,17; 4,3</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-2,94; -0,09</t>
+          <t>-2,75; -0,02</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-4,16; -1,59</t>
+          <t>-4,22; -1,73</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 95,65</t>
+          <t>0,4; 96,79</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-60,67; -3,57</t>
+          <t>-57,75; 0,56</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-70,13; -21,66</t>
+          <t>-70,73; -19,59</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>13,16; 100,17</t>
+          <t>11,43; 101,8</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-39,9; 17,91</t>
+          <t>-40,04; 20,92</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-68,76; -21,63</t>
+          <t>-68,31; -24,88</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>15,59; 79,9</t>
+          <t>17,12; 83,9</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-43,63; -1,56</t>
+          <t>-41,9; 0,14</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-63,84; -31,02</t>
+          <t>-64,81; -33,97</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP11-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP11-Edad-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 8,22</t>
+          <t>0,02; 8,44</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,0; -0,11</t>
+          <t>-6,31; -0,21</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,46; 1,1</t>
+          <t>-5,18; 1,11</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,06; 5,13</t>
+          <t>-4,19; 5,16</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-7,85; -0,09</t>
+          <t>-7,77; 0,03</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-8,03; 0,73</t>
+          <t>-7,75; 1,24</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 5,45</t>
+          <t>-0,74; 5,44</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-5,95; -0,94</t>
+          <t>-5,86; -0,75</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-5,46; -0,0</t>
+          <t>-5,59; -0,04</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-20,59; 487,35</t>
+          <t>-17,25; 494,37</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 63,14</t>
+          <t>-100,0; 77,97</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 161,95</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-59,01; 152,15</t>
+          <t>-54,85; 152,16</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-92,43; 19,63</t>
+          <t>-90,8; 33,32</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 60,91</t>
+          <t>-100,0; 99,21</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-16,84; 191,39</t>
+          <t>-14,45; 176,03</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-88,74; -7,65</t>
+          <t>-89,63; -9,66</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-88,74; 31,45</t>
+          <t>-91,49; 24,94</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 6,5</t>
+          <t>-1,21; 6,3</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,1; 1,02</t>
+          <t>-5,14; 0,67</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,78; 0,25</t>
+          <t>-5,62; 0,19</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,04; 8,16</t>
+          <t>0,18; 8,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,87; 1,34</t>
+          <t>-5,65; 1,08</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-6,74; 0,23</t>
+          <t>-6,56; 0,03</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,91; 6,21</t>
+          <t>0,49; 6,34</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-4,33; 0,11</t>
+          <t>-4,29; 0,33</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-5,36; -0,73</t>
+          <t>-5,4; -0,9</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-14,78; 176,69</t>
+          <t>-18,1; 168,2</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-74,63; 31,06</t>
+          <t>-75,57; 20,14</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-83,62; 17,81</t>
+          <t>-84,34; 8,21</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 165,13</t>
+          <t>0,77; 170,99</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-63,75; 30,01</t>
+          <t>-66,35; 25,76</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-84,62; 7,42</t>
+          <t>-83,26; 6,36</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>11,25; 136,24</t>
+          <t>8,99; 140,36</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-61,22; 2,73</t>
+          <t>-59,68; 7,81</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-77,4; -11,2</t>
+          <t>-78,26; -16,14</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-4,09</t>
+          <t>-4,08</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,0; 5,18</t>
+          <t>-5,68; 5,24</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-8,11; 0,2</t>
+          <t>-8,65; 0,14</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-8,77; 0,05</t>
+          <t>-8,75; -0,15</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,16; 5,45</t>
+          <t>-5,24; 5,4</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-6,31; 2,95</t>
+          <t>-6,21; 3,33</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-9,32; 0,33</t>
+          <t>-8,5; 0,11</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-3,83; 3,37</t>
+          <t>-3,8; 3,61</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-5,95; 0,58</t>
+          <t>-5,76; 0,61</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-7,46; -0,99</t>
+          <t>-7,5; -1,17</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-59,31%</t>
+          <t>-59,12%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-55,75%</t>
+          <t>-55,66%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-53,35; 115,32</t>
+          <t>-56,25; 124,49</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-80,86; 12,27</t>
+          <t>-81,6; 8,96</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-83,54; 24,39</t>
+          <t>-87,57; 13,82</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-50,28; 115,9</t>
+          <t>-52,5; 102,35</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-60,87; 59,96</t>
+          <t>-60,46; 63,44</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-82,63; 22,92</t>
+          <t>-81,44; 8,11</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-41,64; 58,62</t>
+          <t>-41,22; 66,11</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-60,86; 14,48</t>
+          <t>-60,68; 14,16</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-76,39; -13,04</t>
+          <t>-77,28; -14,39</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,93; 6,21</t>
+          <t>-2,04; 5,95</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,46; 4,73</t>
+          <t>-3,03; 4,47</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-5,42; 0,97</t>
+          <t>-5,84; 0,5</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,29; 12,06</t>
+          <t>2,02; 11,92</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 6,73</t>
+          <t>-1,66; 7,0</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-6,18; 0,14</t>
+          <t>-6,22; 0,08</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,41; 7,67</t>
+          <t>1,43; 7,48</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 4,33</t>
+          <t>-1,26; 4,8</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-4,72; -0,51</t>
+          <t>-4,84; -0,18</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-31,42; 177,45</t>
+          <t>-34,34; 189,44</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-41,47; 140,52</t>
+          <t>-48,0; 142,71</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-77,41; 37,91</t>
+          <t>-78,29; 20,35</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>24,2; 274,51</t>
+          <t>21,48; 266,21</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-24,63; 155,52</t>
+          <t>-27,74; 152,85</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-77,81; 11,24</t>
+          <t>-77,62; 11,1</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>16,53; 173,73</t>
+          <t>20,6; 178,7</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-23,45; 98,59</t>
+          <t>-19,81; 110,13</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-69,98; -8,63</t>
+          <t>-69,49; -1,78</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-2,61</t>
+          <t>-2,6</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,04; 4,16</t>
+          <t>0,04; 4,37</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,55; -0,04</t>
+          <t>-3,59; -0,04</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-4,38; -0,85</t>
+          <t>-4,37; -0,96</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,93; 5,68</t>
+          <t>1,09; 5,68</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,93; 1,11</t>
+          <t>-3,05; 0,91</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-5,04; -1,29</t>
+          <t>-5,14; -1,33</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,17; 4,3</t>
+          <t>1,05; 4,19</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-2,75; -0,02</t>
+          <t>-2,61; -0,07</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-4,22; -1,73</t>
+          <t>-4,31; -1,73</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-50,3%</t>
+          <t>-50,24%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-50,48%</t>
+          <t>-50,45%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>0,4; 96,79</t>
+          <t>0,09; 101,47</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-57,75; 0,56</t>
+          <t>-57,18; 1,69</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-70,73; -19,59</t>
+          <t>-70,82; -21,23</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>11,43; 101,8</t>
+          <t>14,44; 101,7</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-40,04; 20,92</t>
+          <t>-40,33; 15,84</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-68,31; -24,88</t>
+          <t>-68,33; -23,97</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>17,12; 83,9</t>
+          <t>14,46; 78,68</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-41,9; 0,14</t>
+          <t>-41,54; -1,14</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-64,81; -33,97</t>
+          <t>-64,94; -32,89</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP11-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP11-Edad-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0,59</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-3,59</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-3,44</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>4,0</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>-2,47</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-2,0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,59</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-3,59</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-3,62</t>
+          <t>-2,23</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-2,88</t>
+          <t>-2,93</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,02; 8,44</t>
+          <t>-3,56; 5,95</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,31; -0,21</t>
+          <t>-7,61; 0,14</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,18; 1,11</t>
+          <t>-7,4; 1,58</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,19; 5,16</t>
+          <t>-0,17; 8,38</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-7,77; 0,03</t>
+          <t>-6,01; 0,11</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-7,75; 1,24</t>
+          <t>-5,69; 0,52</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 5,44</t>
+          <t>-0,99; 5,39</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-5,86; -0,75</t>
+          <t>-6,02; -1,0</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-5,59; -0,04</t>
+          <t>-5,59; 0,19</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>10,2%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-61,94%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-59,35%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>120,21%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>-74,43%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-60,05%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>10,2%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-61,94%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-62,47%</t>
+          <t>-67,07%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-61,94%</t>
+          <t>-63,0%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-17,25; 494,37</t>
+          <t>-46,47; 153,3</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 77,97</t>
+          <t>-91,6; 23,17</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>-100,0; 114,42</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>-15,16; 573,0</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>-100,0; 230,29</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-54,85; 152,16</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-90,8; 33,32</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 99,21</t>
-        </is>
-      </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-14,45; 176,03</t>
+          <t>-19,37; 174,9</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-89,63; -9,66</t>
+          <t>-90,15; -21,33</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-91,49; 24,94</t>
+          <t>-90,44; 32,38</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>4,17</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-1,91</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>-3,34</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>2,54</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>-2,25</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-2,94</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>4,17</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-1,91</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-3,28</t>
+          <t>-2,78</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-3,09</t>
+          <t>-3,06</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 6,3</t>
+          <t>0,34; 8,72</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,14; 0,67</t>
+          <t>-5,02; 1,47</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,62; 0,19</t>
+          <t>-6,56; 0,07</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,18; 8,0</t>
+          <t>-0,83; 6,25</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-5,65; 1,08</t>
+          <t>-5,25; 0,9</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-6,56; 0,03</t>
+          <t>-5,49; 0,6</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,49; 6,34</t>
+          <t>0,86; 6,2</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-4,29; 0,33</t>
+          <t>-4,06; 0,26</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-5,4; -0,9</t>
+          <t>-5,4; -0,7</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>65,87%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-30,15%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>-52,84%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>48,13%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>-42,64%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-55,78%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>65,87%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-30,15%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-51,89%</t>
+          <t>-52,76%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-53,25%</t>
+          <t>-52,64%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-18,1; 168,2</t>
+          <t>2,79; 187,57</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-75,57; 20,14</t>
+          <t>-61,27; 34,87</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-84,34; 8,21</t>
+          <t>-82,49; 9,45</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,77; 170,99</t>
+          <t>-12,66; 163,16</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-66,35; 25,76</t>
+          <t>-75,15; 37,57</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-83,26; 6,36</t>
+          <t>-83,31; 28,98</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,99; 140,36</t>
+          <t>12,2; 132,7</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-59,68; 7,81</t>
+          <t>-58,47; 6,51</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-78,26; -16,14</t>
+          <t>-76,57; -12,05</t>
         </is>
       </c>
     </row>
@@ -1056,34 +1056,34 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>0,07</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-1,35</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>-4,04</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>-0,03</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>-3,58</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>-4,08</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0,07</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-1,35</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-4,17</t>
-        </is>
-      </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
           <t>-0,0</t>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-4,11</t>
+          <t>-4,05</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,68; 5,24</t>
+          <t>-5,21; 5,37</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-8,65; 0,14</t>
+          <t>-6,51; 3,04</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-8,75; -0,15</t>
+          <t>-8,61; 0,94</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,24; 5,4</t>
+          <t>-5,14; 4,88</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-6,21; 3,33</t>
+          <t>-7,94; 0,21</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-8,5; 0,11</t>
+          <t>-8,41; 0,25</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-3,8; 3,61</t>
+          <t>-3,68; 3,65</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-5,76; 0,61</t>
+          <t>-5,92; 0,43</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-7,5; -1,17</t>
+          <t>-7,38; -0,74</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>0,91%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-17,28%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>-51,67%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>-0,47%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>-51,89%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-59,12%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>0,91%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-17,28%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-53,38%</t>
+          <t>-59,13%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-55,66%</t>
+          <t>-54,89%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-56,25; 124,49</t>
+          <t>-51,61; 104,11</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-81,6; 8,96</t>
+          <t>-59,98; 61,26</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-87,57; 13,82</t>
+          <t>-80,71; 26,97</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-52,5; 102,35</t>
+          <t>-55,61; 119,56</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-60,46; 63,44</t>
+          <t>-80,7; 13,28</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-81,44; 8,11</t>
+          <t>-87,44; 17,66</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-41,22; 66,11</t>
+          <t>-40,17; 65,89</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-60,68; 14,16</t>
+          <t>-61,93; 11,06</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-77,28; -14,39</t>
+          <t>-76,79; -9,53</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>7,04</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>2,31</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-2,98</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>1,91</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>0,65</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-2,12</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>7,04</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>2,31</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-2,91</t>
+          <t>-1,81</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-2,53</t>
+          <t>-2,42</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,04; 5,95</t>
+          <t>2,31; 11,47</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,03; 4,47</t>
+          <t>-1,76; 6,78</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-5,84; 0,5</t>
+          <t>-7,14; -0,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,02; 11,92</t>
+          <t>-1,97; 6,26</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 7,0</t>
+          <t>-2,99; 4,9</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-6,22; 0,08</t>
+          <t>-5,31; 0,9</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,43; 7,48</t>
+          <t>1,49; 7,73</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 4,8</t>
+          <t>-1,42; 4,37</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-4,84; -0,18</t>
+          <t>-4,87; -0,4</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>117,28%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>38,5%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-49,7%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>38,45%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>13,16%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-42,88%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>117,28%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>38,5%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-48,54%</t>
+          <t>-36,53%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-46,01%</t>
+          <t>-43,98%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-34,34; 189,44</t>
+          <t>25,58; 269,89</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-48,0; 142,71</t>
+          <t>-25,06; 164,14</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-78,29; 20,35</t>
+          <t>-80,6; 12,51</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>21,48; 266,21</t>
+          <t>-32,61; 202,36</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-27,74; 152,85</t>
+          <t>-46,32; 154,32</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-77,62; 11,1</t>
+          <t>-75,36; 34,34</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>20,6; 178,7</t>
+          <t>19,33; 174,19</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-19,81; 110,13</t>
+          <t>-22,66; 99,59</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-69,49; -1,78</t>
+          <t>-68,71; -5,54</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>3,33</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-0,96</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>-3,26</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>2,09</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>-1,86</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-2,6</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>3,33</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>-0,96</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-3,28</t>
+          <t>-2,45</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-2,94</t>
+          <t>-2,86</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,04; 4,37</t>
+          <t>1,08; 5,69</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,59; -0,04</t>
+          <t>-2,94; 1,02</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-4,37; -0,96</t>
+          <t>-5,24; -1,42</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,09; 5,68</t>
+          <t>-0,05; 4,07</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-3,05; 0,91</t>
+          <t>-3,79; -0,17</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-5,14; -1,33</t>
+          <t>-4,05; -0,66</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,05; 4,19</t>
+          <t>1,08; 4,21</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-2,61; -0,07</t>
+          <t>-2,94; -0,09</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-4,31; -1,73</t>
+          <t>-4,18; -1,53</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>51,76%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-14,92%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>-50,61%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>40,31%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>-35,79%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-50,24%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>51,76%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>-14,92%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-50,94%</t>
+          <t>-47,26%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-50,45%</t>
+          <t>-49,07%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>0,09; 101,47</t>
+          <t>13,16; 100,17</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-57,18; 1,69</t>
+          <t>-39,9; 17,91</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-70,82; -21,23</t>
+          <t>-68,79; -21,19</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>14,44; 101,7</t>
+          <t>-1,32; 95,65</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-40,33; 15,84</t>
+          <t>-60,67; -3,57</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-68,33; -23,97</t>
+          <t>-67,11; -14,14</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>14,46; 78,68</t>
+          <t>15,59; 79,9</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-41,54; -1,14</t>
+          <t>-43,63; -1,56</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-64,94; -32,89</t>
+          <t>-63,21; -30,32</t>
         </is>
       </c>
     </row>
